--- a/docs/data/jp/xlsx/4498.xlsx
+++ b/docs/data/jp/xlsx/4498.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC180"/>
+  <dimension ref="A1:AC187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4231,10 +4234,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>2570</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4269,7 +4274,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>16660400</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5468,7 +5475,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5720,1092 +5727,1207 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>813.921</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>889.202</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>940.538</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>840.799</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>905.682</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>1022.331</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>1087.129</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>1031.078</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>1054.488</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>1138.84</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>1196.419</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>1150.986</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>903.824</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>852.649</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>940.538</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>1087.129</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>1196.419</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>723.158</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>754.672</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>901.1180000000001</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>652.6950000000001</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>932.149</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>955.063</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>1046.188</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>872.648</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>958.02</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1024.714</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>1084.098</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>981.579</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>757.688</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>876.4059999999999</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>901.1180000000001</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>1046.188</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>1084.098</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>477.658</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>485.393</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>483.269</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>507.886</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>533.9059999999999</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>529.612</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>593.293</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>562.91</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>567.7670000000001</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>554.037</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>605.389</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>574.725</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>451.561</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>483.094</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>483.269</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>593.293</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>605.389</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>245.501</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>269.278</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>417.849</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>144.808</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>398.244</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>425.451</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>452.894</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>309.737</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>390.254</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>470.676</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>478.709</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>406.854</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>306.126</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>393.313</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>417.849</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>452.894</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>478.709</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.025</v>
+        <v>477.658</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0.001</v>
+        <v>485.393</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0.027</v>
+        <v>483.269</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0</v>
+        <v>507.886</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.495</v>
+        <v>533.9059999999999</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0</v>
+        <v>529.612</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>2.762</v>
+        <v>593.293</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0</v>
+        <v>562.91</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>5.328</v>
+        <v>567.7670000000001</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0.024</v>
+        <v>554.037</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>6.777</v>
+        <v>605.389</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>1.341</v>
+        <v>574.725</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>0.029</v>
+        <v>451.561</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0.022</v>
+        <v>483.094</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.027</v>
+        <v>483.269</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>2.762</v>
+        <v>593.293</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>6.777</v>
+        <v>605.389</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>245.501</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>269.278</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>417.849</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>144.808</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>398.244</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>425.451</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>452.894</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>309.737</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>390.254</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>470.676</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>478.709</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>406.854</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>306.126</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>393.313</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>417.849</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>452.894</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>478.709</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>지분법이익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>1.255</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>2.566</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>2.987</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>3.456</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>7.864</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>3.503</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>2.798</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>2.591</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>5.479</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>2.619</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>3.318</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>2.305</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>2.987</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>5.479</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>Proceeds From Subsidy NOI</t>
-        </is>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>1.415</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>1.371</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>2.442</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>1.415</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>1.371</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>외환차익</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>0.027</v>
       </c>
       <c r="F87" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="G87" s="22" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H87" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="22" t="n">
+        <v>2.762</v>
+      </c>
       <c r="J87" s="22" t="n">
-        <v>0.5580000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="K87" s="22" t="n">
+        <v>5.328</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>6.777</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>0</v>
+        <v>1.341</v>
+      </c>
+      <c r="T87" s="22" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="U87" s="22" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="V87" s="22" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="W87" s="22" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="X87" s="22" t="n">
+        <v>6.777</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>-0.237</v>
+        <v>0</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>1.468</v>
+        <v>0</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>0.372</v>
+        <v>0.001</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>1.974</v>
+        <v>0</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>3.557</v>
+        <v>0</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>-3.838</v>
+        <v>0</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>0.141</v>
+        <v>0.001</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>2.023</v>
+        <v>0</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>-0.456</v>
+        <v>0</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>0.551</v>
+        <v>0.001</v>
       </c>
       <c r="T88" s="22" t="n">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="U88" s="22" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>1.468</v>
+        <v>0</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>-3.838</v>
+        <v>0</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>-0.456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>지분법이익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>1.829</v>
+        <v>1.255</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>3.737</v>
+        <v>2.566</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>8.196</v>
+        <v>2.987</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>3.831</v>
+        <v>3.456</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>10.332</v>
+        <v>7.864</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>7.06</v>
+        <v>3.503</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>9.858000000000001</v>
+        <v>4.067</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>3.499</v>
+        <v>2.798</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>8.552</v>
+        <v>3.667</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>4.639</v>
+        <v>2.591</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>21.531</v>
+        <v>5.479</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>4.512</v>
+        <v>2.619</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>7.724</v>
+        <v>3.318</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>6.483</v>
+        <v>2.305</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>8.196</v>
+        <v>2.987</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>9.858000000000001</v>
+        <v>4.067</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>21.531</v>
+        <v>5.479</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="D90" s="22" t="n">
-        <v>0.188</v>
+          <t>Proceeds From Subsidy NOI</t>
+        </is>
       </c>
       <c r="E90" s="22" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="F90" s="22" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="G90" s="22" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>0.165</v>
+        <v>1.415</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="22" t="n">
-        <v>0.34</v>
+        <v>1.371</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>0.25</v>
+        <v>2.442</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0.182</v>
+        <v>1.415</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="X90" s="22" t="n">
-        <v>0</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>주식교부비 상각</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="D91" s="22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>0.316</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="U91" s="22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" s="22" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="N91" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>-0.237</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>-3.838</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="M92" s="22" t="n">
+        <v>-0.456</v>
+      </c>
+      <c r="N92" s="22" t="n">
+        <v>0.551</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>0</v>
+        <v>0.582</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>0</v>
+        <v>0.269</v>
+      </c>
+      <c r="V92" s="22" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="W92" s="22" t="n">
+        <v>-3.838</v>
+      </c>
+      <c r="X92" s="22" t="n">
+        <v>-0.456</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>Loss On Disposal Of Treasury Share Acquisition Rights NOE</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>0</v>
+        <v>1.829</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>0</v>
+        <v>3.737</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>0</v>
+        <v>8.196</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>0</v>
+        <v>3.831</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>0</v>
+        <v>10.332</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>0</v>
+        <v>9.858000000000001</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>3.499</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>8.552</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>4.639</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>21.531</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="T93" s="22" t="n">
+        <v>7.724</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>0</v>
+        <v>6.483</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>0</v>
+        <v>8.196</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>0</v>
+        <v>9.858000000000001</v>
+      </c>
+      <c r="X93" s="22" t="n">
+        <v>21.531</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>Loss On Liquidation Of Subsidiaries NOE</t>
-        </is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>0.205</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0</v>
+        <v>0.182</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="22" t="n">
+        <v>0.34</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V94" s="22" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="X94" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>Consumption Tax Difference NOE</t>
-        </is>
+          <t>주식교부비 상각</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="N95" s="22" t="n">
-        <v>0.544</v>
+        <v>0</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="U95" s="22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
-      </c>
-      <c r="C96" s="22" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="D96" s="22" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="E96" s="22" t="n">
-        <v>-0.063</v>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="G96" s="22" t="n">
-        <v>-0.319</v>
-      </c>
-      <c r="H96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="22" t="n">
-        <v>4.189</v>
-      </c>
-      <c r="L96" s="22" t="n">
-        <v>11.036</v>
-      </c>
-      <c r="M96" s="22" t="n">
-        <v>-1.984</v>
-      </c>
-      <c r="N96" s="22" t="n">
-        <v>2.13</v>
+          <t>상장 관련 비용</t>
+        </is>
       </c>
       <c r="T96" s="22" t="n">
-        <v>-0.496</v>
+        <v>0</v>
       </c>
       <c r="U96" s="22" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V96" s="22" t="n">
-        <v>-0.063</v>
-      </c>
-      <c r="W96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" s="22" t="n">
-        <v>-1.984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>Loss On Disposal Of Treasury Share Acquisition Rights NOE</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="F97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="22" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <v>1.397</v>
-      </c>
-      <c r="M97" s="22" t="n">
-        <v>-0.8139999999999999</v>
-      </c>
-      <c r="T97" s="22" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="U97" s="22" t="n">
-        <v>0.676</v>
+        <v>0</v>
       </c>
       <c r="V97" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="W97" s="22" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="X97" s="22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>0.575</v>
+          <t>Loss On Liquidation Of Subsidiaries NOE</t>
+        </is>
       </c>
       <c r="D98" s="22" t="n">
-        <v>3.791</v>
+        <v>0</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>-0.144</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>5.315</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>11.443</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>13.171</v>
-      </c>
-      <c r="N98" s="22" t="n">
-        <v>2.675</v>
-      </c>
-      <c r="T98" s="22" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U98" s="22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V98" s="22" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>13.171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
-        <v>246.755</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>269.224</v>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>425.6</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>148.132</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>408.72</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>432.344</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>459.184</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>313.057</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>393.489</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>463.874</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>487.068</v>
-      </c>
-      <c r="N99" s="12" t="n">
-        <v>408.691</v>
-      </c>
-      <c r="T99" s="12" t="n">
-        <v>313.69</v>
-      </c>
-      <c r="U99" s="12" t="n">
-        <v>397.886</v>
-      </c>
-      <c r="V99" s="12" t="n">
-        <v>425.6</v>
-      </c>
-      <c r="W99" s="12" t="n">
-        <v>459.184</v>
-      </c>
-      <c r="X99" s="12" t="n">
-        <v>487.068</v>
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>Consumption Tax Difference NOE</t>
+        </is>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>0.544</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>-0.319</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>4.189</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>11.036</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>-1.984</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>2.13</v>
       </c>
       <c r="T100" s="22" t="n">
-        <v>74.684</v>
+        <v>-0.496</v>
       </c>
       <c r="U100" s="22" t="n">
-        <v>0</v>
+        <v>0.667</v>
+      </c>
+      <c r="V100" s="22" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>-1.984</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>Head Office Transfer Cost EL</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="F101" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H101" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>25.66</v>
+        <v>0.004</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>98.15300000000001</v>
+        <v>0.076</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>14.102</v>
+        <v>0.135</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>0</v>
+        <v>1.397</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="22" t="n">
-        <v>0</v>
+        <v>-0.8139999999999999</v>
+      </c>
+      <c r="T101" s="22" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="U101" s="22" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="V101" s="22" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>25.66</v>
+        <v>0.004</v>
       </c>
       <c r="X101" s="22" t="n">
-        <v>0</v>
+        <v>-0.8139999999999999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>3.791</v>
+      </c>
+      <c r="E102" s="22" t="n">
+        <v>0.445</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>0</v>
+        <v>0.508</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>0</v>
+        <v>-0.144</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>25.66</v>
+        <v>3.57</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>98.15300000000001</v>
+        <v>0.18</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>14.102</v>
+        <v>5.315</v>
       </c>
       <c r="L102" s="22" t="n">
-        <v>0</v>
+        <v>11.443</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>53.629</v>
+        <v>13.171</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>0</v>
+        <v>2.675</v>
       </c>
       <c r="T102" s="22" t="n">
-        <v>74.684</v>
+        <v>0.16</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>0</v>
+        <v>1.91</v>
+      </c>
+      <c r="V102" s="22" t="n">
+        <v>0.445</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>25.66</v>
+        <v>3.57</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>53.629</v>
+        <v>13.171</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>법인세차감전 순이익</t>
+          <t>경상이익</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
@@ -6815,7 +6937,7 @@
         <v>269.224</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>80.37</v>
+        <v>425.6</v>
       </c>
       <c r="F103" s="12" t="n">
         <v>148.132</v>
@@ -6827,513 +6949,432 @@
         <v>432.344</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>433.523</v>
+        <v>459.184</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>214.903</v>
+        <v>313.057</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>379.388</v>
+        <v>393.489</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>463.873</v>
+        <v>463.874</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>433.44</v>
+        <v>487.068</v>
       </c>
       <c r="N103" s="12" t="n">
         <v>408.691</v>
       </c>
       <c r="T103" s="12" t="n">
-        <v>239.006</v>
+        <v>313.69</v>
       </c>
       <c r="U103" s="12" t="n">
         <v>397.886</v>
       </c>
       <c r="V103" s="12" t="n">
-        <v>80.37</v>
+        <v>425.6</v>
       </c>
       <c r="W103" s="12" t="n">
-        <v>433.523</v>
+        <v>459.184</v>
       </c>
       <c r="X103" s="12" t="n">
-        <v>433.44</v>
+        <v>487.068</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="n">
-        <v>110.668</v>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>46.047</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>178.231</v>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>5.499</v>
-      </c>
-      <c r="G104" s="22" t="n">
-        <v>156.627</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>50.383</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>214.591</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>2.379</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>147.932</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>93.529</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>257.076</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>9.175000000000001</v>
-      </c>
-      <c r="T104" s="22" t="n">
-        <v>132.437</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>179.891</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>178.231</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>214.591</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>257.076</v>
+      <c r="A104" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G104" s="17">
+        <f>IF(OR(G103="",C103=""),"",IF(C103&lt;=0,"",IFERROR(G103/C103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H104" s="17">
+        <f>IF(OR(H103="",D103=""),"",IF(D103&lt;=0,"",IFERROR(H103/D103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I104" s="17">
+        <f>IF(OR(I103="",E103=""),"",IF(E103&lt;=0,"",IFERROR(I103/E103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J104" s="17">
+        <f>IF(OR(J103="",F103=""),"",IF(F103&lt;=0,"",IFERROR(J103/F103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF(OR(K103="",G103=""),"",IF(G103&lt;=0,"",IFERROR(K103/G103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L104" s="17">
+        <f>IF(OR(L103="",H103=""),"",IF(H103&lt;=0,"",IFERROR(L103/H103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M104" s="17">
+        <f>IF(OR(M103="",I103=""),"",IF(I103&lt;=0,"",IFERROR(M103/I103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N104" s="17">
+        <f>IF(OR(N103="",J103=""),"",IF(J103&lt;=0,"",IFERROR(N103/J103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T104" s="17">
+        <f>IF(OR(T103="",S103=""),"",IF(S103&lt;=0,"",IFERROR(T103/S103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U104" s="17">
+        <f>IF(OR(U103="",T103=""),"",IF(T103&lt;=0,"",IFERROR(U103/T103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V104" s="17">
+        <f>IF(OR(V103="",U103=""),"",IF(U103&lt;=0,"",IFERROR(V103/U103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W104" s="17">
+        <f>IF(OR(W103="",V103=""),"",IF(V103&lt;=0,"",IFERROR(W103/V103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X104" s="17">
+        <f>IF(OR(X103="",W103=""),"",IF(W103&lt;=0,"",IFERROR(X103/W103-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="n">
-        <v>-29.458</v>
-      </c>
-      <c r="D105" s="22" t="n">
-        <v>43.431</v>
-      </c>
-      <c r="E105" s="22" t="n">
-        <v>-154.812</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>38.734</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>-53.302</v>
-      </c>
-      <c r="H105" s="22" t="n">
-        <v>86.83499999999999</v>
-      </c>
-      <c r="I105" s="22" t="n">
-        <v>-46.333</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>87.83499999999999</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>-19.408</v>
-      </c>
-      <c r="L105" s="22" t="n">
-        <v>57.093</v>
-      </c>
-      <c r="M105" s="22" t="n">
-        <v>-124.676</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>130.019</v>
+          <t>고정자산 제각손실</t>
+        </is>
       </c>
       <c r="T105" s="22" t="n">
-        <v>-53.246</v>
+        <v>74.684</v>
       </c>
       <c r="U105" s="22" t="n">
-        <v>-57.59</v>
-      </c>
-      <c r="V105" s="22" t="n">
-        <v>-154.812</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>-46.333</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>-124.676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="n">
-        <v>81.20999999999999</v>
-      </c>
-      <c r="D106" s="22" t="n">
-        <v>89.479</v>
-      </c>
-      <c r="E106" s="22" t="n">
-        <v>23.418</v>
+          <t>Head Office Transfer Cost EL</t>
+        </is>
       </c>
       <c r="F106" s="22" t="n">
-        <v>44.234</v>
+        <v>0</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>103.324</v>
+        <v>0</v>
       </c>
       <c r="H106" s="22" t="n">
-        <v>137.218</v>
+        <v>0</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>168.259</v>
+        <v>25.66</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>90.215</v>
+        <v>98.15300000000001</v>
       </c>
       <c r="K106" s="22" t="n">
-        <v>128.524</v>
+        <v>14.102</v>
       </c>
       <c r="L106" s="22" t="n">
-        <v>150.622</v>
+        <v>0</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>132.399</v>
+        <v>0</v>
       </c>
       <c r="N106" s="22" t="n">
-        <v>139.195</v>
-      </c>
-      <c r="T106" s="22" t="n">
-        <v>79.19</v>
-      </c>
-      <c r="U106" s="22" t="n">
-        <v>122.301</v>
-      </c>
-      <c r="V106" s="22" t="n">
-        <v>23.418</v>
+        <v>0</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>168.259</v>
+        <v>25.66</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>132.399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>165.545</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>179.746</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>56.952</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>103.897</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>305.396</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>295.126</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>265.265</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>124.688</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>250.864</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>313.251</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>301.04</v>
-      </c>
-      <c r="N107" s="12" t="n">
-        <v>269.495</v>
-      </c>
-      <c r="T107" s="12" t="n">
-        <v>159.816</v>
-      </c>
-      <c r="U107" s="12" t="n">
-        <v>275.585</v>
-      </c>
-      <c r="V107" s="12" t="n">
-        <v>56.952</v>
-      </c>
-      <c r="W107" s="12" t="n">
-        <v>265.265</v>
-      </c>
-      <c r="X107" s="12" t="n">
-        <v>301.04</v>
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>98.15300000000001</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>14.102</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>53.629</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>74.684</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>53.629</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C108" s="12" t="n">
-        <v>165.545</v>
+        <v>246.755</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>179.746</v>
+        <v>269.224</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>56.952</v>
+        <v>80.37</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>103.897</v>
+        <v>148.132</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>305.396</v>
+        <v>408.72</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>295.126</v>
+        <v>432.344</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>265.265</v>
+        <v>433.523</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>124.688</v>
+        <v>214.903</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>250.864</v>
+        <v>379.388</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>313.251</v>
+        <v>463.873</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>301.04</v>
+        <v>433.44</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>269.495</v>
+        <v>408.691</v>
       </c>
       <c r="T108" s="12" t="n">
-        <v>159.816</v>
+        <v>239.006</v>
       </c>
       <c r="U108" s="12" t="n">
-        <v>275.585</v>
+        <v>397.886</v>
       </c>
       <c r="V108" s="12" t="n">
-        <v>56.952</v>
+        <v>80.37</v>
       </c>
       <c r="W108" s="12" t="n">
-        <v>265.265</v>
+        <v>433.523</v>
       </c>
       <c r="X108" s="12" t="n">
-        <v>301.04</v>
+        <v>433.44</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n">
+        <v>110.668</v>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>46.047</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>178.231</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>5.499</v>
+      </c>
+      <c r="G109" s="22" t="n">
+        <v>156.627</v>
+      </c>
+      <c r="H109" s="22" t="n">
+        <v>50.383</v>
+      </c>
+      <c r="I109" s="22" t="n">
+        <v>214.591</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <v>147.932</v>
+      </c>
+      <c r="L109" s="22" t="n">
+        <v>93.529</v>
+      </c>
+      <c r="M109" s="22" t="n">
+        <v>257.076</v>
+      </c>
+      <c r="N109" s="22" t="n">
+        <v>9.175000000000001</v>
+      </c>
+      <c r="T109" s="22" t="n">
+        <v>132.437</v>
+      </c>
+      <c r="U109" s="22" t="n">
+        <v>179.891</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>178.231</v>
+      </c>
+      <c r="W109" s="22" t="n">
+        <v>214.591</v>
+      </c>
+      <c r="X109" s="22" t="n">
+        <v>257.076</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B110" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="18" t="n"/>
-      <c r="I110" s="18" t="n"/>
-      <c r="J110" s="18" t="n"/>
-      <c r="K110" s="18" t="n"/>
-      <c r="L110" s="18" t="n"/>
-      <c r="M110" s="18" t="n"/>
-      <c r="N110" s="18" t="n"/>
-      <c r="O110" s="18" t="n"/>
-      <c r="P110" s="18" t="n"/>
-      <c r="Q110" s="18" t="n"/>
-      <c r="R110" s="18" t="n"/>
-      <c r="S110" s="18" t="n"/>
-      <c r="T110" s="18" t="n"/>
-      <c r="U110" s="18" t="n"/>
-      <c r="V110" s="18" t="n"/>
-      <c r="W110" s="18" t="n"/>
-      <c r="X110" s="18" t="n"/>
-      <c r="Y110" s="18" t="n"/>
-      <c r="Z110" s="18" t="n"/>
-      <c r="AA110" s="18" t="n"/>
-      <c r="AB110" s="18" t="n"/>
-      <c r="AC110" s="18" t="n"/>
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>-29.458</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>43.431</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>-154.812</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>38.734</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>-53.302</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>86.83499999999999</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>-46.333</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>87.83499999999999</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>-19.408</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>57.093</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>-124.676</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>130.019</v>
+      </c>
+      <c r="T110" s="22" t="n">
+        <v>-53.246</v>
+      </c>
+      <c r="U110" s="22" t="n">
+        <v>-57.59</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>-154.812</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>-46.333</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>-124.676</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M111" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N111" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O111" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P111" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q111" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R111" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S111" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T111" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U111" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V111" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W111" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X111" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y111" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z111" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA111" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB111" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC111" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A111" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n">
+        <v>81.20999999999999</v>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>89.479</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>23.418</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>44.234</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>103.324</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>137.218</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>168.259</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>90.215</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>128.524</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>150.622</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>132.399</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>139.195</v>
+      </c>
+      <c r="T111" s="22" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="U111" s="22" t="n">
+        <v>122.301</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>23.418</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>168.259</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>132.399</v>
       </c>
     </row>
     <row r="112">
@@ -7395,1955 +7436,2189 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="20" t="inlineStr">
+      <c r="A113" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G113" s="17">
+        <f>IF(OR(G112="",C112=""),"",IF(C112&lt;=0,"",IFERROR(G112/C112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H113" s="17">
+        <f>IF(OR(H112="",D112=""),"",IF(D112&lt;=0,"",IFERROR(H112/D112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I113" s="17">
+        <f>IF(OR(I112="",E112=""),"",IF(E112&lt;=0,"",IFERROR(I112/E112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J113" s="17">
+        <f>IF(OR(J112="",F112=""),"",IF(F112&lt;=0,"",IFERROR(J112/F112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF(OR(K112="",G112=""),"",IF(G112&lt;=0,"",IFERROR(K112/G112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L113" s="17">
+        <f>IF(OR(L112="",H112=""),"",IF(H112&lt;=0,"",IFERROR(L112/H112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M113" s="17">
+        <f>IF(OR(M112="",I112=""),"",IF(I112&lt;=0,"",IFERROR(M112/I112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N113" s="17">
+        <f>IF(OR(N112="",J112=""),"",IF(J112&lt;=0,"",IFERROR(N112/J112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T113" s="17">
+        <f>IF(OR(T112="",S112=""),"",IF(S112&lt;=0,"",IFERROR(T112/S112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U113" s="17">
+        <f>IF(OR(U112="",T112=""),"",IF(T112&lt;=0,"",IFERROR(U112/T112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V113" s="17">
+        <f>IF(OR(V112="",U112=""),"",IF(U112&lt;=0,"",IFERROR(V112/U112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W113" s="17">
+        <f>IF(OR(W112="",V112=""),"",IF(V112&lt;=0,"",IFERROR(W112/V112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X113" s="17">
+        <f>IF(OR(X112="",W112=""),"",IF(W112&lt;=0,"",IFERROR(X112/W112-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>165.545</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>179.746</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>56.952</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>103.897</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>305.396</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>295.126</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>265.265</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>124.688</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>250.864</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>313.251</v>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>301.04</v>
+      </c>
+      <c r="N114" s="12" t="n">
+        <v>269.495</v>
+      </c>
+      <c r="T114" s="12" t="n">
+        <v>159.816</v>
+      </c>
+      <c r="U114" s="12" t="n">
+        <v>275.585</v>
+      </c>
+      <c r="V114" s="12" t="n">
+        <v>56.952</v>
+      </c>
+      <c r="W114" s="12" t="n">
+        <v>265.265</v>
+      </c>
+      <c r="X114" s="12" t="n">
+        <v>301.04</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G115" s="17">
+        <f>IF(OR(G114="",C114=""),"",IF(C114&lt;=0,"",IFERROR(G114/C114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H115" s="17">
+        <f>IF(OR(H114="",D114=""),"",IF(D114&lt;=0,"",IFERROR(H114/D114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I115" s="17">
+        <f>IF(OR(I114="",E114=""),"",IF(E114&lt;=0,"",IFERROR(I114/E114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J115" s="17">
+        <f>IF(OR(J114="",F114=""),"",IF(F114&lt;=0,"",IFERROR(J114/F114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF(OR(K114="",G114=""),"",IF(G114&lt;=0,"",IFERROR(K114/G114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L115" s="17">
+        <f>IF(OR(L114="",H114=""),"",IF(H114&lt;=0,"",IFERROR(L114/H114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M115" s="17">
+        <f>IF(OR(M114="",I114=""),"",IF(I114&lt;=0,"",IFERROR(M114/I114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N115" s="17">
+        <f>IF(OR(N114="",J114=""),"",IF(J114&lt;=0,"",IFERROR(N114/J114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T115" s="17">
+        <f>IF(OR(T114="",S114=""),"",IF(S114&lt;=0,"",IFERROR(T114/S114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U115" s="17">
+        <f>IF(OR(U114="",T114=""),"",IF(T114&lt;=0,"",IFERROR(U114/T114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V115" s="17">
+        <f>IF(OR(V114="",U114=""),"",IF(U114&lt;=0,"",IFERROR(V114/U114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W115" s="17">
+        <f>IF(OR(W114="",V114=""),"",IF(V114&lt;=0,"",IFERROR(W114/V114-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X115" s="17">
+        <f>IF(OR(X114="",W114=""),"",IF(W114&lt;=0,"",IFERROR(X114/W114-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B117" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+      <c r="G117" s="18" t="n"/>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+      <c r="J117" s="18" t="n"/>
+      <c r="K117" s="18" t="n"/>
+      <c r="L117" s="18" t="n"/>
+      <c r="M117" s="18" t="n"/>
+      <c r="N117" s="18" t="n"/>
+      <c r="O117" s="18" t="n"/>
+      <c r="P117" s="18" t="n"/>
+      <c r="Q117" s="18" t="n"/>
+      <c r="R117" s="18" t="n"/>
+      <c r="S117" s="18" t="n"/>
+      <c r="T117" s="18" t="n"/>
+      <c r="U117" s="18" t="n"/>
+      <c r="V117" s="18" t="n"/>
+      <c r="W117" s="18" t="n"/>
+      <c r="X117" s="18" t="n"/>
+      <c r="Y117" s="18" t="n"/>
+      <c r="Z117" s="18" t="n"/>
+      <c r="AA117" s="18" t="n"/>
+      <c r="AB117" s="18" t="n"/>
+      <c r="AC117" s="18" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O118" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P118" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q118" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S118" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T118" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U118" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V118" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W118" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X118" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y118" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z118" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA118" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB118" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC118" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>165.545</v>
+      </c>
+      <c r="D119" s="12" t="n">
+        <v>179.746</v>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>56.952</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>103.897</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>305.396</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>295.126</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>265.265</v>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>124.688</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>250.864</v>
+      </c>
+      <c r="L119" s="12" t="n">
+        <v>313.251</v>
+      </c>
+      <c r="M119" s="12" t="n">
+        <v>301.04</v>
+      </c>
+      <c r="N119" s="12" t="n">
+        <v>269.495</v>
+      </c>
+      <c r="T119" s="12" t="n">
+        <v>159.816</v>
+      </c>
+      <c r="U119" s="12" t="n">
+        <v>275.585</v>
+      </c>
+      <c r="V119" s="12" t="n">
+        <v>56.952</v>
+      </c>
+      <c r="W119" s="12" t="n">
+        <v>265.265</v>
+      </c>
+      <c r="X119" s="12" t="n">
+        <v>301.04</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="H113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="22" t="n">
+      <c r="H120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="22" t="n">
         <v>-1.7</v>
       </c>
-      <c r="L113" s="22" t="n">
+      <c r="L120" s="22" t="n">
         <v>7.063</v>
       </c>
-      <c r="M113" s="22" t="n">
+      <c r="M120" s="22" t="n">
         <v>-3.678</v>
       </c>
-      <c r="N113" s="22" t="n">
+      <c r="N120" s="22" t="n">
         <v>-0.5590000000000001</v>
       </c>
-      <c r="W113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="22" t="n">
+      <c r="W120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="22" t="n">
         <v>-3.678</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>해외사업환산조정</t>
         </is>
       </c>
-      <c r="C114" s="22" t="n">
+      <c r="C121" s="22" t="n">
         <v>0.44</v>
       </c>
-      <c r="D114" s="22" t="n">
+      <c r="D121" s="22" t="n">
         <v>0.235</v>
       </c>
-      <c r="E114" s="22" t="n">
+      <c r="E121" s="22" t="n">
         <v>-0.343</v>
       </c>
-      <c r="F114" s="22" t="n">
+      <c r="F121" s="22" t="n">
         <v>0.429</v>
       </c>
-      <c r="G114" s="22" t="n">
+      <c r="G121" s="22" t="n">
         <v>0.443</v>
       </c>
-      <c r="H114" s="22" t="n">
+      <c r="H121" s="22" t="n">
         <v>-4.185</v>
       </c>
-      <c r="I114" s="22" t="n">
+      <c r="I121" s="22" t="n">
         <v>4.049</v>
       </c>
-      <c r="J114" s="22" t="n">
+      <c r="J121" s="22" t="n">
         <v>-0.434</v>
       </c>
-      <c r="K114" s="22" t="n">
+      <c r="K121" s="22" t="n">
         <v>-0.243</v>
       </c>
-      <c r="L114" s="22" t="n">
+      <c r="L121" s="22" t="n">
         <v>0.211</v>
       </c>
-      <c r="M114" s="22" t="n">
+      <c r="M121" s="22" t="n">
         <v>0.433</v>
       </c>
-      <c r="N114" s="22" t="n">
+      <c r="N121" s="22" t="n">
         <v>0.197</v>
       </c>
-      <c r="T114" s="22" t="n">
+      <c r="T121" s="22" t="n">
         <v>0.234</v>
       </c>
-      <c r="U114" s="22" t="n">
+      <c r="U121" s="22" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="V114" s="22" t="n">
+      <c r="V121" s="22" t="n">
         <v>-0.343</v>
       </c>
-      <c r="W114" s="22" t="n">
+      <c r="W121" s="22" t="n">
         <v>4.049</v>
       </c>
-      <c r="X114" s="22" t="n">
+      <c r="X121" s="22" t="n">
         <v>0.433</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="D115" s="22" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>-0.343</v>
-      </c>
-      <c r="F115" s="22" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="H115" s="22" t="n">
-        <v>-4.185</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="J115" s="22" t="n">
-        <v>-0.434</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>-1.943</v>
-      </c>
-      <c r="L115" s="22" t="n">
-        <v>7.273</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>-3.244</v>
-      </c>
-      <c r="N115" s="22" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="T115" s="22" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>-0.343</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>-3.244</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>165.985</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>179.98</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>104.327</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>305.839</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>290.94</v>
-      </c>
-      <c r="I116" s="12" t="n">
-        <v>265.985</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>124.253</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>248.922</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>320.525</v>
-      </c>
-      <c r="M116" s="12" t="n">
-        <v>297.795</v>
-      </c>
-      <c r="N116" s="12" t="n">
-        <v>269.134</v>
-      </c>
-      <c r="T116" s="12" t="n">
-        <v>160.049</v>
-      </c>
-      <c r="U116" s="12" t="n">
-        <v>275.656</v>
-      </c>
-      <c r="V116" s="12" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="W116" s="12" t="n">
-        <v>265.985</v>
-      </c>
-      <c r="X116" s="12" t="n">
-        <v>297.795</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n">
-        <v>165.985</v>
-      </c>
-      <c r="D117" s="12" t="n">
-        <v>179.98</v>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="F117" s="12" t="n">
-        <v>104.327</v>
-      </c>
-      <c r="G117" s="12" t="n">
-        <v>305.839</v>
-      </c>
-      <c r="H117" s="12" t="n">
-        <v>290.94</v>
-      </c>
-      <c r="I117" s="12" t="n">
-        <v>265.985</v>
-      </c>
-      <c r="J117" s="12" t="n">
-        <v>124.253</v>
-      </c>
-      <c r="K117" s="12" t="n">
-        <v>248.922</v>
-      </c>
-      <c r="L117" s="12" t="n">
-        <v>320.525</v>
-      </c>
-      <c r="M117" s="12" t="n">
-        <v>297.795</v>
-      </c>
-      <c r="N117" s="12" t="n">
-        <v>269.134</v>
-      </c>
-      <c r="T117" s="12" t="n">
-        <v>160.049</v>
-      </c>
-      <c r="U117" s="12" t="n">
-        <v>275.656</v>
-      </c>
-      <c r="V117" s="12" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="W117" s="12" t="n">
-        <v>265.985</v>
-      </c>
-      <c r="X117" s="12" t="n">
-        <v>297.795</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="18" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B119" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="18" t="n"/>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-      <c r="J119" s="18" t="n"/>
-      <c r="K119" s="18" t="n"/>
-      <c r="L119" s="18" t="n"/>
-      <c r="M119" s="18" t="n"/>
-      <c r="N119" s="18" t="n"/>
-      <c r="O119" s="18" t="n"/>
-      <c r="P119" s="18" t="n"/>
-      <c r="Q119" s="18" t="n"/>
-      <c r="R119" s="18" t="n"/>
-      <c r="S119" s="18" t="n"/>
-      <c r="T119" s="18" t="n"/>
-      <c r="U119" s="18" t="n"/>
-      <c r="V119" s="18" t="n"/>
-      <c r="W119" s="18" t="n"/>
-      <c r="X119" s="18" t="n"/>
-      <c r="Y119" s="18" t="n"/>
-      <c r="Z119" s="18" t="n"/>
-      <c r="AA119" s="18" t="n"/>
-      <c r="AB119" s="18" t="n"/>
-      <c r="AC119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M120" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N120" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O120" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P120" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q120" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R120" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S120" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T120" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U120" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V120" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W120" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X120" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y120" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z120" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA120" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB120" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC120" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="n">
-        <v>426.554</v>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v>776.148</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>556.852</v>
-      </c>
-      <c r="I121" s="12" t="n">
-        <v>1422.719</v>
-      </c>
-      <c r="K121" s="12" t="n">
-        <v>594.2910000000001</v>
-      </c>
-      <c r="M121" s="12" t="n">
-        <v>1491.604</v>
-      </c>
-      <c r="R121" s="12" t="n">
-        <v>521.721</v>
-      </c>
-      <c r="S121" s="12" t="n">
-        <v>630.394</v>
-      </c>
-      <c r="T121" s="12" t="n">
-        <v>797.792</v>
-      </c>
-      <c r="U121" s="12" t="n">
-        <v>1065.587</v>
-      </c>
-      <c r="V121" s="12" t="n">
-        <v>776.148</v>
-      </c>
-      <c r="W121" s="12" t="n">
-        <v>1422.719</v>
-      </c>
-      <c r="X121" s="12" t="n">
-        <v>1491.604</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>기타포괄손익 합계</t>
         </is>
       </c>
       <c r="C122" s="22" t="n">
-        <v>290.191</v>
+        <v>0.44</v>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>0.235</v>
       </c>
       <c r="E122" s="22" t="n">
-        <v>591.528</v>
+        <v>-0.343</v>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>0.429</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>249.814</v>
+        <v>0.443</v>
+      </c>
+      <c r="H122" s="22" t="n">
+        <v>-4.185</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>571.92</v>
+        <v>0.721</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>-0.434</v>
       </c>
       <c r="K122" s="22" t="n">
-        <v>291.956</v>
+        <v>-1.943</v>
+      </c>
+      <c r="L122" s="22" t="n">
+        <v>7.273</v>
       </c>
       <c r="M122" s="22" t="n">
-        <v>583.325</v>
-      </c>
-      <c r="R122" s="22" t="n">
-        <v>303.653</v>
-      </c>
-      <c r="S122" s="22" t="n">
-        <v>364.43</v>
+        <v>-3.244</v>
+      </c>
+      <c r="N122" s="22" t="n">
+        <v>-0.361</v>
       </c>
       <c r="T122" s="22" t="n">
-        <v>501.812</v>
+        <v>0.234</v>
       </c>
       <c r="U122" s="22" t="n">
-        <v>556.34</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>591.528</v>
+        <v>-0.343</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>571.92</v>
+        <v>0.721</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>583.325</v>
+        <v>-3.244</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="E123" s="22" t="n">
-        <v>345.23</v>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>15.323</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="22" t="n">
-        <v>345.23</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>0</v>
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="n">
+        <v>165.985</v>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>104.327</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>305.839</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>290.94</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>265.985</v>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>124.253</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>248.922</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>320.525</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>297.795</v>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>269.134</v>
+      </c>
+      <c r="T123" s="12" t="n">
+        <v>160.049</v>
+      </c>
+      <c r="U123" s="12" t="n">
+        <v>275.656</v>
+      </c>
+      <c r="V123" s="12" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="W123" s="12" t="n">
+        <v>265.985</v>
+      </c>
+      <c r="X123" s="12" t="n">
+        <v>297.795</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C124" s="22" t="n">
-        <v>6.279</v>
-      </c>
-      <c r="E124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="G124" s="22" t="n">
-        <v>6.279</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="K124" s="22" t="n">
-        <v>6.279</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>9.417999999999999</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>12.558</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="C125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="22" t="n">
-        <v>6.139</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>9.417</v>
-      </c>
-      <c r="K125" s="22" t="n">
-        <v>-0.658</v>
-      </c>
-      <c r="M125" s="22" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="T125" s="22" t="n">
-        <v>-0.582</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>3.091</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>9.417</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>-0.165</v>
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>165.985</v>
+      </c>
+      <c r="D124" s="12" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>104.327</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>305.839</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>290.94</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>265.985</v>
+      </c>
+      <c r="J124" s="12" t="n">
+        <v>124.253</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>248.922</v>
+      </c>
+      <c r="L124" s="12" t="n">
+        <v>320.525</v>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>297.795</v>
+      </c>
+      <c r="N124" s="12" t="n">
+        <v>269.134</v>
+      </c>
+      <c r="T124" s="12" t="n">
+        <v>160.049</v>
+      </c>
+      <c r="U124" s="12" t="n">
+        <v>275.656</v>
+      </c>
+      <c r="V124" s="12" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="W124" s="12" t="n">
+        <v>265.985</v>
+      </c>
+      <c r="X124" s="12" t="n">
+        <v>297.795</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C126" s="22" t="n">
-        <v>-8.281000000000001</v>
-      </c>
-      <c r="E126" s="22" t="n">
-        <v>-6.501</v>
-      </c>
-      <c r="G126" s="22" t="n">
-        <v>24.236</v>
-      </c>
-      <c r="I126" s="22" t="n">
-        <v>80.789</v>
-      </c>
-      <c r="K126" s="22" t="n">
-        <v>-42.919</v>
-      </c>
-      <c r="M126" s="22" t="n">
-        <v>63.588</v>
-      </c>
-      <c r="R126" s="22" t="n">
-        <v>-6.745</v>
-      </c>
-      <c r="S126" s="22" t="n">
-        <v>67.16800000000001</v>
-      </c>
-      <c r="T126" s="22" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="U126" s="22" t="n">
-        <v>-25.586</v>
-      </c>
-      <c r="V126" s="22" t="n">
-        <v>-6.501</v>
-      </c>
-      <c r="W126" s="22" t="n">
-        <v>80.789</v>
-      </c>
-      <c r="X126" s="22" t="n">
-        <v>63.588</v>
-      </c>
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B126" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+      <c r="J126" s="18" t="n"/>
+      <c r="K126" s="18" t="n"/>
+      <c r="L126" s="18" t="n"/>
+      <c r="M126" s="18" t="n"/>
+      <c r="N126" s="18" t="n"/>
+      <c r="O126" s="18" t="n"/>
+      <c r="P126" s="18" t="n"/>
+      <c r="Q126" s="18" t="n"/>
+      <c r="R126" s="18" t="n"/>
+      <c r="S126" s="18" t="n"/>
+      <c r="T126" s="18" t="n"/>
+      <c r="U126" s="18" t="n"/>
+      <c r="V126" s="18" t="n"/>
+      <c r="W126" s="18" t="n"/>
+      <c r="X126" s="18" t="n"/>
+      <c r="Y126" s="18" t="n"/>
+      <c r="Z126" s="18" t="n"/>
+      <c r="AA126" s="18" t="n"/>
+      <c r="AB126" s="18" t="n"/>
+      <c r="AC126" s="18" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C127" s="22" t="n">
-        <v>-10.203</v>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>-2.853</v>
-      </c>
-      <c r="G127" s="22" t="n">
-        <v>-6.198</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>15.258</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>-18.104</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>8.444000000000001</v>
-      </c>
-      <c r="R127" s="22" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="S127" s="22" t="n">
-        <v>24.697</v>
-      </c>
-      <c r="T127" s="22" t="n">
-        <v>3.381</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>-12.39</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>-2.853</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>15.258</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>8.444000000000001</v>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q127" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S127" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T127" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U127" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V127" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W127" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X127" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y127" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z127" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA127" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB127" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC127" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>주식급여 충당금 증감</t>
-        </is>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>52.18</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>52.18</v>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>426.554</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>776.148</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>556.852</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>1422.719</v>
+      </c>
+      <c r="K128" s="12" t="n">
+        <v>594.2910000000001</v>
+      </c>
+      <c r="M128" s="12" t="n">
+        <v>1491.604</v>
+      </c>
+      <c r="R128" s="12" t="n">
+        <v>521.721</v>
+      </c>
+      <c r="S128" s="12" t="n">
+        <v>630.394</v>
+      </c>
+      <c r="T128" s="12" t="n">
+        <v>797.792</v>
+      </c>
+      <c r="U128" s="12" t="n">
+        <v>1065.587</v>
+      </c>
+      <c r="V128" s="12" t="n">
+        <v>776.148</v>
+      </c>
+      <c r="W128" s="12" t="n">
+        <v>1422.719</v>
+      </c>
+      <c r="X128" s="12" t="n">
+        <v>1491.604</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>임원 주식급여 충당금 증감</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n">
+        <v>290.191</v>
+      </c>
+      <c r="E129" s="22" t="n">
+        <v>591.528</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>0</v>
+        <v>249.814</v>
       </c>
       <c r="I129" s="22" t="n">
-        <v>0</v>
+        <v>571.92</v>
       </c>
       <c r="K129" s="22" t="n">
-        <v>5.218</v>
+        <v>291.956</v>
       </c>
       <c r="M129" s="22" t="n">
-        <v>10.957</v>
+        <v>583.325</v>
+      </c>
+      <c r="R129" s="22" t="n">
+        <v>303.653</v>
+      </c>
+      <c r="S129" s="22" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="T129" s="22" t="n">
+        <v>501.812</v>
+      </c>
+      <c r="U129" s="22" t="n">
+        <v>556.34</v>
+      </c>
+      <c r="V129" s="22" t="n">
+        <v>591.528</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>0</v>
+        <v>571.92</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>10.957</v>
+        <v>583.325</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>기타 충당금 증감</t>
-        </is>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="n">
+        <v>345.23</v>
       </c>
       <c r="I130" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M130" s="22" t="n">
-        <v>24.269</v>
+      <c r="R130" s="22" t="n">
+        <v>15.323</v>
+      </c>
+      <c r="S130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>345.23</v>
       </c>
       <c r="W130" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>24.269</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
+          <t>영업권 상각</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n">
+        <v>6.279</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>12.558</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>6.279</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>0</v>
+        <v>12.558</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>6.279</v>
       </c>
       <c r="M131" s="22" t="n">
-        <v>-6.414</v>
+        <v>12.558</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="22" t="n">
+        <v>9.417999999999999</v>
+      </c>
+      <c r="T131" s="22" t="n">
+        <v>12.558</v>
+      </c>
+      <c r="U131" s="22" t="n">
+        <v>12.558</v>
+      </c>
+      <c r="V131" s="22" t="n">
+        <v>12.558</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>0</v>
+        <v>12.558</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>-6.414</v>
+        <v>12.558</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="C132" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E132" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="G132" s="22" t="n">
+        <v>6.139</v>
+      </c>
       <c r="I132" s="22" t="n">
-        <v>4.974</v>
+        <v>9.417</v>
+      </c>
+      <c r="K132" s="22" t="n">
+        <v>-0.658</v>
       </c>
       <c r="M132" s="22" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="R132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" s="22" t="n">
-        <v>54.305</v>
+        <v>-0.165</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>77.953</v>
+        <v>-0.582</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>0</v>
+        <v>3.091</v>
       </c>
       <c r="V132" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>4.974</v>
+        <v>9.417</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>0.097</v>
+        <v>-0.165</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n">
+        <v>-8.281000000000001</v>
+      </c>
+      <c r="E133" s="22" t="n">
+        <v>-6.501</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>24.236</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>80.789</v>
+      </c>
+      <c r="K133" s="22" t="n">
+        <v>-42.919</v>
+      </c>
+      <c r="M133" s="22" t="n">
+        <v>63.588</v>
       </c>
       <c r="R133" s="22" t="n">
-        <v>-115.028</v>
+        <v>-6.745</v>
       </c>
       <c r="S133" s="22" t="n">
-        <v>-60.32</v>
+        <v>67.16800000000001</v>
       </c>
       <c r="T133" s="22" t="n">
-        <v>0</v>
+        <v>-4.7</v>
+      </c>
+      <c r="U133" s="22" t="n">
+        <v>-25.586</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>-6.501</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>80.789</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>63.588</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
+          <t>임원 상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>-10.203</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.054</v>
+        <v>-2.853</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>-6.198</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>-3.258</v>
+        <v>15.258</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>-18.104</v>
+      </c>
+      <c r="M134" s="22" t="n">
+        <v>8.444000000000001</v>
+      </c>
+      <c r="R134" s="22" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="S134" s="22" t="n">
+        <v>24.697</v>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>3.381</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>-12.39</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>-0.054</v>
+        <v>-2.853</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>-3.258</v>
+        <v>15.258</v>
+      </c>
+      <c r="X134" s="22" t="n">
+        <v>8.444000000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>주식급여 충당금 증감</t>
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>-0.496</v>
+        <v>0</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>-3.258</v>
+        <v>0</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>-5.329</v>
+        <v>26.09</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>-12.13</v>
+        <v>52.18</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>-3.258</v>
+        <v>0</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>-12.13</v>
+        <v>52.18</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>지분법손익</t>
-        </is>
-      </c>
-      <c r="C136" s="22" t="n">
-        <v>-4.516</v>
-      </c>
-      <c r="E136" s="22" t="n">
-        <v>-10.069</v>
+          <t>임원 주식급여 충당금 증감</t>
+        </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>-18.89</v>
+        <v>0</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>-6.465</v>
+        <v>5.218</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>-14.535</v>
-      </c>
-      <c r="R136" s="22" t="n">
-        <v>-0.124</v>
-      </c>
-      <c r="S136" s="22" t="n">
-        <v>-12.206</v>
-      </c>
-      <c r="T136" s="22" t="n">
-        <v>-7.944</v>
-      </c>
-      <c r="U136" s="22" t="n">
-        <v>-10.076</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>-10.069</v>
+        <v>10.957</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-18.89</v>
+        <v>0</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>-14.535</v>
+        <v>10.957</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>29.977</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>0</v>
+          <t>기타 충당금 증감</t>
+        </is>
+      </c>
+      <c r="I137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="22" t="n">
+        <v>24.269</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>24.269</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="C138" s="22" t="n">
-        <v>89.54900000000001</v>
-      </c>
-      <c r="S138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" s="22" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="U138" s="22" t="n">
-        <v>-20.049</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
+      </c>
+      <c r="I138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>-6.414</v>
+      </c>
+      <c r="W138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="22" t="n">
+        <v>-6.414</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>Head Office Relocation Expenses Ope CF</t>
-        </is>
-      </c>
-      <c r="G139" s="22" t="n">
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="E139" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="22" t="n">
-        <v>112.255</v>
+        <v>4.974</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>112.255</v>
+        <v>0.097</v>
+      </c>
+      <c r="R139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="22" t="n">
+        <v>54.305</v>
+      </c>
+      <c r="T139" s="22" t="n">
+        <v>77.953</v>
+      </c>
+      <c r="U139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>0</v>
+        <v>4.974</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>112.255</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="C140" s="22" t="n">
-        <v>89.54900000000001</v>
-      </c>
-      <c r="E140" s="22" t="n">
-        <v>-190.12</v>
-      </c>
-      <c r="G140" s="22" t="n">
-        <v>317.013</v>
-      </c>
-      <c r="I140" s="22" t="n">
-        <v>-45.295</v>
-      </c>
-      <c r="K140" s="22" t="n">
-        <v>122.193</v>
-      </c>
-      <c r="M140" s="22" t="n">
-        <v>-279.425</v>
-      </c>
-      <c r="U140" s="22" t="n">
-        <v>-20.049</v>
-      </c>
-      <c r="V140" s="22" t="n">
-        <v>-190.12</v>
-      </c>
-      <c r="W140" s="22" t="n">
-        <v>-45.295</v>
-      </c>
-      <c r="X140" s="22" t="n">
-        <v>-279.425</v>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="R140" s="22" t="n">
+        <v>-115.028</v>
+      </c>
+      <c r="S140" s="22" t="n">
+        <v>-60.32</v>
+      </c>
+      <c r="T140" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="n">
-        <v>0.192</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="E141" s="22" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="G141" s="22" t="n">
-        <v>-3.06</v>
+        <v>-0.054</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="K141" s="22" t="n">
-        <v>-6.652</v>
-      </c>
-      <c r="M141" s="22" t="n">
-        <v>-0.062</v>
-      </c>
-      <c r="R141" s="22" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="S141" s="22" t="n">
-        <v>14.265</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>0.764</v>
+        <v>-3.258</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>0.194</v>
+        <v>-0.054</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="X141" s="22" t="n">
-        <v>-0.062</v>
+        <v>-3.258</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>선급비용 증감</t>
-        </is>
-      </c>
-      <c r="C142" s="22" t="n">
-        <v>-44.632</v>
-      </c>
-      <c r="E142" s="22" t="n">
-        <v>-41.808</v>
+          <t>이자·배당금 수익</t>
+        </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>-67.922</v>
+        <v>-0.496</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>-55.739</v>
+        <v>-3.258</v>
       </c>
       <c r="K142" s="22" t="n">
-        <v>-35.527</v>
+        <v>-5.329</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>-113.13</v>
-      </c>
-      <c r="R142" s="22" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="S142" s="22" t="n">
-        <v>-16.176</v>
-      </c>
-      <c r="T142" s="22" t="n">
-        <v>-7.731</v>
-      </c>
-      <c r="U142" s="22" t="n">
-        <v>-29.539</v>
-      </c>
-      <c r="V142" s="22" t="n">
-        <v>-41.808</v>
+        <v>-12.13</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-55.739</v>
+        <v>-3.258</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-113.13</v>
+        <v>-12.13</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>지분법손익</t>
         </is>
       </c>
       <c r="C143" s="22" t="n">
-        <v>-33.102</v>
+        <v>-4.516</v>
       </c>
       <c r="E143" s="22" t="n">
-        <v>58.248</v>
+        <v>-10.069</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>-49.388</v>
+        <v>-11.32</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>3.633</v>
+        <v>-18.89</v>
       </c>
       <c r="K143" s="22" t="n">
-        <v>-29.339</v>
+        <v>-6.465</v>
       </c>
       <c r="M143" s="22" t="n">
-        <v>6.038</v>
+        <v>-14.535</v>
       </c>
       <c r="R143" s="22" t="n">
-        <v>60.96</v>
+        <v>-0.124</v>
       </c>
       <c r="S143" s="22" t="n">
-        <v>11.351</v>
+        <v>-12.206</v>
       </c>
       <c r="T143" s="22" t="n">
-        <v>56.489</v>
+        <v>-7.944</v>
       </c>
       <c r="U143" s="22" t="n">
-        <v>-96.373</v>
+        <v>-10.076</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>58.248</v>
+        <v>-10.069</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>3.633</v>
+        <v>-18.89</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>6.038</v>
+        <v>-14.535</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
-        </is>
-      </c>
-      <c r="C144" s="22" t="n">
-        <v>241.089</v>
+          <t>투자유가증권 평가손익</t>
+        </is>
+      </c>
+      <c r="R144" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>0</v>
+        <v>29.977</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>270.07</v>
-      </c>
-      <c r="U144" s="22" t="n">
-        <v>15.648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>매출채권·계약자산 증감</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>241.089</v>
-      </c>
-      <c r="E145" s="22" t="n">
-        <v>58.264</v>
-      </c>
-      <c r="G145" s="22" t="n">
-        <v>688.561</v>
-      </c>
-      <c r="I145" s="22" t="n">
-        <v>238.444</v>
-      </c>
-      <c r="K145" s="22" t="n">
-        <v>336.328</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>67.267</v>
+        <v>89.54900000000001</v>
+      </c>
+      <c r="S145" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" s="22" t="n">
+        <v>40.99</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>15.648</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>58.264</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>238.444</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>67.267</v>
+        <v>-20.049</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Trade Receivables Other Ope CF</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="n">
-        <v>-46.511</v>
-      </c>
-      <c r="E146" s="22" t="n">
-        <v>-35.627</v>
+          <t>Head Office Relocation Expenses Ope CF</t>
+        </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>7.387</v>
+        <v>0</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>16.693</v>
+        <v>0</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>-22.529</v>
+        <v>112.255</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>-7.179</v>
-      </c>
-      <c r="R146" s="22" t="n">
-        <v>-0.273</v>
-      </c>
-      <c r="S146" s="22" t="n">
-        <v>-135.765</v>
-      </c>
-      <c r="T146" s="22" t="n">
-        <v>-13.836</v>
-      </c>
-      <c r="U146" s="22" t="n">
-        <v>12.183</v>
-      </c>
-      <c r="V146" s="22" t="n">
-        <v>-35.627</v>
+        <v>112.255</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>16.693</v>
+        <v>0</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-7.179</v>
+        <v>112.255</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Trade Payables Other Ope CF</t>
+          <t>매출채권·계약자산 증감</t>
         </is>
       </c>
       <c r="C147" s="22" t="n">
-        <v>25.843</v>
+        <v>89.54900000000001</v>
       </c>
       <c r="E147" s="22" t="n">
-        <v>53.14</v>
+        <v>-190.12</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>-47.019</v>
+        <v>317.013</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>19.701</v>
+        <v>-45.295</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>12.237</v>
+        <v>122.193</v>
       </c>
       <c r="M147" s="22" t="n">
-        <v>95.639</v>
-      </c>
-      <c r="R147" s="22" t="n">
-        <v>-38.243</v>
-      </c>
-      <c r="S147" s="22" t="n">
-        <v>19.827</v>
-      </c>
-      <c r="T147" s="22" t="n">
-        <v>1.394</v>
+        <v>-279.425</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>-0.625</v>
+        <v>-20.049</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>53.14</v>
+        <v>-190.12</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>19.701</v>
+        <v>-45.295</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>95.639</v>
+        <v>-279.425</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>-43.907</v>
+        <v>0.192</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-29.671</v>
+        <v>0.194</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>2.143</v>
+        <v>-3.06</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>61.795</v>
+        <v>0.038</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>-101.262</v>
+        <v>-6.652</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>-56.94</v>
+        <v>-0.062</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>10.159</v>
+        <v>-1.4</v>
       </c>
       <c r="S148" s="22" t="n">
-        <v>-3.187</v>
+        <v>14.265</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>54.316</v>
+        <v>-1.08</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>-26.988</v>
+        <v>0.764</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>-29.671</v>
+        <v>0.194</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>61.795</v>
+        <v>0.038</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>-56.94</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>선수수익 증감</t>
-        </is>
+          <t>선급비용 증감</t>
+        </is>
+      </c>
+      <c r="C149" s="22" t="n">
+        <v>-44.632</v>
+      </c>
+      <c r="E149" s="22" t="n">
+        <v>-41.808</v>
+      </c>
+      <c r="G149" s="22" t="n">
+        <v>-67.922</v>
+      </c>
+      <c r="I149" s="22" t="n">
+        <v>-55.739</v>
+      </c>
+      <c r="K149" s="22" t="n">
+        <v>-35.527</v>
+      </c>
+      <c r="M149" s="22" t="n">
+        <v>-113.13</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>100.577</v>
+        <v>48.52</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>264.963</v>
+        <v>-16.176</v>
       </c>
       <c r="T149" s="22" t="n">
-        <v>0</v>
+        <v>-7.731</v>
+      </c>
+      <c r="U149" s="22" t="n">
+        <v>-29.539</v>
+      </c>
+      <c r="V149" s="22" t="n">
+        <v>-41.808</v>
+      </c>
+      <c r="W149" s="22" t="n">
+        <v>-55.739</v>
+      </c>
+      <c r="X149" s="22" t="n">
+        <v>-113.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C150" s="22" t="n">
-        <v>2.213</v>
+        <v>-33.102</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>2.703</v>
+        <v>58.248</v>
       </c>
       <c r="G150" s="22" t="n">
-        <v>1.405</v>
+        <v>-49.388</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>3.105</v>
+        <v>3.633</v>
       </c>
       <c r="K150" s="22" t="n">
-        <v>5.076</v>
+        <v>-29.339</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>14.24</v>
+        <v>6.038</v>
       </c>
       <c r="R150" s="22" t="n">
-        <v>1.033</v>
+        <v>60.96</v>
       </c>
       <c r="S150" s="22" t="n">
-        <v>4.377</v>
+        <v>11.351</v>
       </c>
       <c r="T150" s="22" t="n">
-        <v>4.285</v>
+        <v>56.489</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>2.405</v>
+        <v>-96.373</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>2.703</v>
+        <v>58.248</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>3.105</v>
+        <v>3.633</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>14.24</v>
+        <v>6.038</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C151" s="22" t="n">
-        <v>890.756</v>
-      </c>
-      <c r="E151" s="22" t="n">
-        <v>1581.309</v>
-      </c>
-      <c r="G151" s="22" t="n">
-        <v>1674.425</v>
-      </c>
-      <c r="I151" s="22" t="n">
-        <v>2337.865</v>
-      </c>
-      <c r="K151" s="22" t="n">
-        <v>1243.137</v>
-      </c>
-      <c r="M151" s="22" t="n">
-        <v>2052.484</v>
-      </c>
-      <c r="R151" s="22" t="n">
-        <v>896.533</v>
+        <v>241.089</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>1267.521</v>
+        <v>0</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>1785.171</v>
+        <v>270.07</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>1446.95</v>
-      </c>
-      <c r="V151" s="22" t="n">
-        <v>1581.309</v>
-      </c>
-      <c r="W151" s="22" t="n">
-        <v>2337.865</v>
-      </c>
-      <c r="X151" s="22" t="n">
-        <v>2052.484</v>
+        <v>15.648</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C152" s="22" t="n">
-        <v>6.69</v>
+        <v>241.089</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>6.717</v>
+        <v>58.264</v>
       </c>
       <c r="G152" s="22" t="n">
-        <v>7.159</v>
+        <v>688.561</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>9.920999999999999</v>
+        <v>238.444</v>
       </c>
       <c r="K152" s="22" t="n">
-        <v>11.993</v>
+        <v>336.328</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>17.987</v>
-      </c>
-      <c r="R152" s="22" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="S152" s="22" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="T152" s="22" t="n">
-        <v>0.139</v>
+        <v>67.267</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>0.079</v>
+        <v>15.648</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>6.717</v>
+        <v>58.264</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>9.920999999999999</v>
+        <v>238.444</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>17.987</v>
+        <v>67.267</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>Decrease Increase In Trade Receivables Other Ope CF</t>
         </is>
       </c>
       <c r="C153" s="22" t="n">
-        <v>-0.432</v>
+        <v>-46.511</v>
       </c>
       <c r="E153" s="22" t="n">
-        <v>-0.802</v>
+        <v>-35.627</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>-0.348</v>
+        <v>7.387</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-0.674</v>
+        <v>16.693</v>
       </c>
       <c r="K153" s="22" t="n">
-        <v>-0.103</v>
+        <v>-22.529</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>-0.103</v>
+        <v>-7.179</v>
       </c>
       <c r="R153" s="22" t="n">
-        <v>-2.319</v>
+        <v>-0.273</v>
       </c>
       <c r="S153" s="22" t="n">
-        <v>-1.859</v>
+        <v>-135.765</v>
       </c>
       <c r="T153" s="22" t="n">
-        <v>-1.491</v>
+        <v>-13.836</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>-1.136</v>
+        <v>12.183</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>-0.802</v>
+        <v>-35.627</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-0.674</v>
+        <v>16.693</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>-0.103</v>
+        <v>-7.179</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
-        </is>
+          <t>Increase Decrease In Trade Payables Other Ope CF</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="n">
+        <v>25.843</v>
+      </c>
+      <c r="E154" s="22" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="G154" s="22" t="n">
+        <v>-47.019</v>
+      </c>
+      <c r="I154" s="22" t="n">
+        <v>19.701</v>
+      </c>
+      <c r="K154" s="22" t="n">
+        <v>12.237</v>
+      </c>
+      <c r="M154" s="22" t="n">
+        <v>95.639</v>
+      </c>
+      <c r="R154" s="22" t="n">
+        <v>-38.243</v>
       </c>
       <c r="S154" s="22" t="n">
-        <v>0</v>
+        <v>19.827</v>
       </c>
       <c r="T154" s="22" t="n">
-        <v>129.49</v>
+        <v>1.394</v>
       </c>
       <c r="U154" s="22" t="n">
-        <v>0</v>
+        <v>-0.625</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>19.701</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>95.639</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>Payments For Head Office Relocation Expenses Ope CF</t>
-        </is>
+          <t>미지급 소비세 증감</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="n">
+        <v>-43.907</v>
+      </c>
+      <c r="E155" s="22" t="n">
+        <v>-29.671</v>
       </c>
       <c r="G155" s="22" t="n">
-        <v>0</v>
+        <v>2.143</v>
       </c>
       <c r="I155" s="22" t="n">
-        <v>0</v>
+        <v>61.795</v>
       </c>
       <c r="K155" s="22" t="n">
-        <v>-41.237</v>
+        <v>-101.262</v>
       </c>
       <c r="M155" s="22" t="n">
-        <v>-41.237</v>
+        <v>-56.94</v>
+      </c>
+      <c r="R155" s="22" t="n">
+        <v>10.159</v>
+      </c>
+      <c r="S155" s="22" t="n">
+        <v>-3.187</v>
+      </c>
+      <c r="T155" s="22" t="n">
+        <v>54.316</v>
+      </c>
+      <c r="U155" s="22" t="n">
+        <v>-26.988</v>
+      </c>
+      <c r="V155" s="22" t="n">
+        <v>-29.671</v>
       </c>
       <c r="W155" s="22" t="n">
-        <v>0</v>
+        <v>61.795</v>
       </c>
       <c r="X155" s="22" t="n">
-        <v>-41.237</v>
+        <v>-56.94</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
-        </is>
-      </c>
-      <c r="C156" s="22" t="n">
-        <v>-203.304</v>
-      </c>
-      <c r="E156" s="22" t="n">
-        <v>-365.379</v>
-      </c>
-      <c r="G156" s="22" t="n">
-        <v>-182.224</v>
-      </c>
-      <c r="I156" s="22" t="n">
-        <v>-353.788</v>
-      </c>
-      <c r="K156" s="22" t="n">
-        <v>-255.888</v>
-      </c>
-      <c r="M156" s="22" t="n">
-        <v>-475.851</v>
+          <t>선수수익 증감</t>
+        </is>
       </c>
       <c r="R156" s="22" t="n">
-        <v>-82.518</v>
+        <v>100.577</v>
       </c>
       <c r="S156" s="22" t="n">
-        <v>-147.043</v>
+        <v>264.963</v>
       </c>
       <c r="T156" s="22" t="n">
-        <v>-308.858</v>
-      </c>
-      <c r="U156" s="22" t="n">
-        <v>-232.027</v>
-      </c>
-      <c r="V156" s="22" t="n">
-        <v>-365.379</v>
-      </c>
-      <c r="W156" s="22" t="n">
-        <v>-353.788</v>
-      </c>
-      <c r="X156" s="22" t="n">
-        <v>-475.851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="n">
-        <v>693.7089999999999</v>
-      </c>
-      <c r="E157" s="12" t="n">
-        <v>1221.845</v>
-      </c>
-      <c r="G157" s="12" t="n">
-        <v>1499.012</v>
-      </c>
-      <c r="I157" s="12" t="n">
-        <v>1993.324</v>
-      </c>
-      <c r="K157" s="12" t="n">
-        <v>957.901</v>
-      </c>
-      <c r="M157" s="12" t="n">
-        <v>1553.279</v>
-      </c>
-      <c r="R157" s="12" t="n">
-        <v>811.902</v>
-      </c>
-      <c r="S157" s="12" t="n">
-        <v>1119.267</v>
-      </c>
-      <c r="T157" s="12" t="n">
-        <v>1604.45</v>
-      </c>
-      <c r="U157" s="12" t="n">
-        <v>1213.866</v>
-      </c>
-      <c r="V157" s="12" t="n">
-        <v>1221.845</v>
-      </c>
-      <c r="W157" s="12" t="n">
-        <v>1993.324</v>
-      </c>
-      <c r="X157" s="12" t="n">
-        <v>1553.279</v>
+      <c r="A157" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C157" s="22" t="n">
+        <v>2.213</v>
+      </c>
+      <c r="E157" s="22" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="I157" s="22" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="K157" s="22" t="n">
+        <v>5.076</v>
+      </c>
+      <c r="M157" s="22" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="R157" s="22" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="S157" s="22" t="n">
+        <v>4.377</v>
+      </c>
+      <c r="T157" s="22" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="U157" s="22" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="X157" s="22" t="n">
+        <v>14.24</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C158" s="22" t="n">
+        <v>890.756</v>
+      </c>
+      <c r="E158" s="22" t="n">
+        <v>1581.309</v>
+      </c>
+      <c r="G158" s="22" t="n">
+        <v>1674.425</v>
+      </c>
+      <c r="I158" s="22" t="n">
+        <v>2337.865</v>
+      </c>
+      <c r="K158" s="22" t="n">
+        <v>1243.137</v>
+      </c>
+      <c r="M158" s="22" t="n">
+        <v>2052.484</v>
       </c>
       <c r="R158" s="22" t="n">
-        <v>0</v>
+        <v>896.533</v>
       </c>
       <c r="S158" s="22" t="n">
-        <v>-13.5</v>
+        <v>1267.521</v>
       </c>
       <c r="T158" s="22" t="n">
-        <v>0</v>
+        <v>1785.171</v>
+      </c>
+      <c r="U158" s="22" t="n">
+        <v>1446.95</v>
+      </c>
+      <c r="V158" s="22" t="n">
+        <v>1581.309</v>
+      </c>
+      <c r="W158" s="22" t="n">
+        <v>2337.865</v>
+      </c>
+      <c r="X158" s="22" t="n">
+        <v>2052.484</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C159" s="22" t="n">
-        <v>0</v>
+        <v>6.69</v>
+      </c>
+      <c r="E159" s="22" t="n">
+        <v>6.717</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>-100</v>
+        <v>7.159</v>
+      </c>
+      <c r="I159" s="22" t="n">
+        <v>9.920999999999999</v>
       </c>
       <c r="K159" s="22" t="n">
-        <v>-150.59</v>
+        <v>11.993</v>
+      </c>
+      <c r="M159" s="22" t="n">
+        <v>17.987</v>
       </c>
       <c r="R159" s="22" t="n">
-        <v>-123.539</v>
+        <v>0.206</v>
       </c>
       <c r="S159" s="22" t="n">
-        <v>0</v>
+        <v>0.648</v>
+      </c>
+      <c r="T159" s="22" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="U159" s="22" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="V159" s="22" t="n">
+        <v>6.717</v>
+      </c>
+      <c r="W159" s="22" t="n">
+        <v>9.920999999999999</v>
+      </c>
+      <c r="X159" s="22" t="n">
+        <v>17.987</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>자회사 주식 취득</t>
-        </is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="n">
+        <v>-0.432</v>
+      </c>
+      <c r="E160" s="22" t="n">
+        <v>-0.802</v>
+      </c>
+      <c r="G160" s="22" t="n">
+        <v>-0.348</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>-0.674</v>
+      </c>
+      <c r="K160" s="22" t="n">
+        <v>-0.103</v>
+      </c>
+      <c r="M160" s="22" t="n">
+        <v>-0.103</v>
       </c>
       <c r="R160" s="22" t="n">
-        <v>0</v>
+        <v>-2.319</v>
       </c>
       <c r="S160" s="22" t="n">
-        <v>-87.88800000000001</v>
+        <v>-1.859</v>
+      </c>
+      <c r="T160" s="22" t="n">
+        <v>-1.491</v>
+      </c>
+      <c r="U160" s="22" t="n">
+        <v>-1.136</v>
+      </c>
+      <c r="V160" s="22" t="n">
+        <v>-0.802</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>-0.674</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>-0.103</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
-      </c>
-      <c r="R161" s="22" t="n">
-        <v>2</v>
+          <t>보조금 수취</t>
+        </is>
       </c>
       <c r="S161" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" s="22" t="n">
+        <v>129.49</v>
+      </c>
+      <c r="U161" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
-        </is>
-      </c>
-      <c r="C162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="22" t="n">
-        <v>0</v>
+          <t>Payments For Head Office Relocation Expenses Ope CF</t>
+        </is>
       </c>
       <c r="G162" s="22" t="n">
-        <v>20.698</v>
+        <v>0</v>
       </c>
       <c r="I162" s="22" t="n">
-        <v>20.698</v>
+        <v>0</v>
       </c>
       <c r="K162" s="22" t="n">
-        <v>0</v>
+        <v>-41.237</v>
       </c>
       <c r="M162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="T162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" s="22" t="n">
-        <v>0</v>
+        <v>-41.237</v>
       </c>
       <c r="W162" s="22" t="n">
-        <v>20.698</v>
+        <v>0</v>
       </c>
       <c r="X162" s="22" t="n">
-        <v>0</v>
+        <v>-41.237</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="C163" s="22" t="n">
-        <v>-53.477</v>
+        <v>-203.304</v>
       </c>
       <c r="E163" s="22" t="n">
-        <v>-136.063</v>
+        <v>-365.379</v>
       </c>
       <c r="G163" s="22" t="n">
-        <v>-84.90300000000001</v>
+        <v>-182.224</v>
       </c>
       <c r="I163" s="22" t="n">
-        <v>-260.42</v>
+        <v>-353.788</v>
       </c>
       <c r="K163" s="22" t="n">
-        <v>-233.385</v>
+        <v>-255.888</v>
       </c>
       <c r="M163" s="22" t="n">
-        <v>-413.665</v>
+        <v>-475.851</v>
       </c>
       <c r="R163" s="22" t="n">
-        <v>-141.578</v>
+        <v>-82.518</v>
       </c>
       <c r="S163" s="22" t="n">
-        <v>-167.086</v>
+        <v>-147.043</v>
       </c>
       <c r="T163" s="22" t="n">
-        <v>-91.95399999999999</v>
+        <v>-308.858</v>
       </c>
       <c r="U163" s="22" t="n">
-        <v>-101.021</v>
+        <v>-232.027</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>-136.063</v>
+        <v>-365.379</v>
       </c>
       <c r="W163" s="22" t="n">
-        <v>-260.42</v>
+        <v>-353.788</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>-413.665</v>
+        <v>-475.851</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="20" t="inlineStr">
-        <is>
-          <t>무형자산 취득</t>
-        </is>
-      </c>
-      <c r="C164" s="22" t="n">
-        <v>-222.074</v>
-      </c>
-      <c r="E164" s="22" t="n">
-        <v>-435.475</v>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>-230.33</v>
-      </c>
-      <c r="I164" s="22" t="n">
-        <v>-419.969</v>
-      </c>
-      <c r="K164" s="22" t="n">
-        <v>-165.035</v>
-      </c>
-      <c r="M164" s="22" t="n">
-        <v>-536.47</v>
-      </c>
-      <c r="R164" s="22" t="n">
-        <v>-423.425</v>
-      </c>
-      <c r="S164" s="22" t="n">
-        <v>-833.599</v>
-      </c>
-      <c r="T164" s="22" t="n">
-        <v>-390.956</v>
-      </c>
-      <c r="U164" s="22" t="n">
-        <v>-339.392</v>
-      </c>
-      <c r="V164" s="22" t="n">
-        <v>-435.475</v>
-      </c>
-      <c r="W164" s="22" t="n">
-        <v>-419.969</v>
-      </c>
-      <c r="X164" s="22" t="n">
-        <v>-536.47</v>
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="n">
+        <v>693.7089999999999</v>
+      </c>
+      <c r="E164" s="12" t="n">
+        <v>1221.845</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>1499.012</v>
+      </c>
+      <c r="I164" s="12" t="n">
+        <v>1993.324</v>
+      </c>
+      <c r="K164" s="12" t="n">
+        <v>957.901</v>
+      </c>
+      <c r="M164" s="12" t="n">
+        <v>1553.279</v>
+      </c>
+      <c r="R164" s="12" t="n">
+        <v>811.902</v>
+      </c>
+      <c r="S164" s="12" t="n">
+        <v>1119.267</v>
+      </c>
+      <c r="T164" s="12" t="n">
+        <v>1604.45</v>
+      </c>
+      <c r="U164" s="12" t="n">
+        <v>1213.866</v>
+      </c>
+      <c r="V164" s="12" t="n">
+        <v>1221.845</v>
+      </c>
+      <c r="W164" s="12" t="n">
+        <v>1993.324</v>
+      </c>
+      <c r="X164" s="12" t="n">
+        <v>1553.279</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
+          <t>정기예금 예입</t>
+        </is>
+      </c>
+      <c r="R165" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="S165" s="22" t="n">
-        <v>-87.88800000000001</v>
+        <v>-13.5</v>
       </c>
       <c r="T165" s="22" t="n">
         <v>0</v>
@@ -9352,561 +9627,757 @@
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
-      </c>
-      <c r="E166" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" s="22" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="V166" s="22" t="n">
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="K166" s="22" t="n">
+        <v>-150.59</v>
+      </c>
+      <c r="R166" s="22" t="n">
+        <v>-123.539</v>
+      </c>
+      <c r="S166" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>Collection Of Short Term Loans Receivable Inv CF</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="22" t="n">
-        <v>0</v>
+          <t>자회사 주식 취득</t>
+        </is>
       </c>
       <c r="R167" s="22" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="S167" s="22" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="T167" s="22" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="U167" s="22" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="V167" s="22" t="n">
-        <v>0</v>
+        <v>-87.88800000000001</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Short Term And Long Term Investment Securities Inv CF</t>
-        </is>
-      </c>
-      <c r="E168" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M168" s="22" t="n">
-        <v>-790.184</v>
-      </c>
-      <c r="V168" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W168" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="X168" s="22" t="n">
-        <v>-790.184</v>
+          <t>투자유가증권 매각</t>
+        </is>
+      </c>
+      <c r="R168" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S168" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각·상환 수입</t>
-        </is>
+          <t>정기예금 인출</t>
+        </is>
+      </c>
+      <c r="C169" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="22" t="n">
+        <v>20.698</v>
       </c>
       <c r="I169" s="22" t="n">
+        <v>20.698</v>
+      </c>
+      <c r="K169" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M169" s="22" t="n">
-        <v>157.004</v>
+        <v>0</v>
+      </c>
+      <c r="R169" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="T169" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="W169" s="22" t="n">
-        <v>0</v>
+        <v>20.698</v>
       </c>
       <c r="X169" s="22" t="n">
-        <v>157.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>보증금 납입</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C170" s="22" t="n">
-        <v>0</v>
+        <v>-53.477</v>
       </c>
       <c r="E170" s="22" t="n">
-        <v>0</v>
+        <v>-136.063</v>
       </c>
       <c r="G170" s="22" t="n">
-        <v>-110.807</v>
+        <v>-84.90300000000001</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>-111.146</v>
+        <v>-260.42</v>
       </c>
       <c r="K170" s="22" t="n">
-        <v>-0.21</v>
+        <v>-233.385</v>
       </c>
       <c r="M170" s="22" t="n">
-        <v>-0.21</v>
+        <v>-413.665</v>
       </c>
       <c r="R170" s="22" t="n">
-        <v>-3.483</v>
+        <v>-141.578</v>
       </c>
       <c r="S170" s="22" t="n">
-        <v>-0.008</v>
+        <v>-167.086</v>
       </c>
       <c r="T170" s="22" t="n">
-        <v>0</v>
+        <v>-91.95399999999999</v>
       </c>
       <c r="U170" s="22" t="n">
-        <v>-0.92</v>
+        <v>-101.021</v>
       </c>
       <c r="V170" s="22" t="n">
-        <v>0</v>
+        <v>-136.063</v>
       </c>
       <c r="W170" s="22" t="n">
-        <v>-111.146</v>
+        <v>-260.42</v>
       </c>
       <c r="X170" s="22" t="n">
-        <v>-0.21</v>
+        <v>-413.665</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>보증금 회수</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C171" s="22" t="n">
-        <v>0.08</v>
+        <v>-222.074</v>
       </c>
       <c r="E171" s="22" t="n">
-        <v>0.08</v>
+        <v>-435.475</v>
       </c>
       <c r="G171" s="22" t="n">
-        <v>0</v>
+        <v>-230.33</v>
       </c>
       <c r="I171" s="22" t="n">
-        <v>0</v>
+        <v>-419.969</v>
       </c>
       <c r="K171" s="22" t="n">
-        <v>169.036</v>
+        <v>-165.035</v>
       </c>
       <c r="M171" s="22" t="n">
-        <v>169.036</v>
+        <v>-536.47</v>
       </c>
       <c r="R171" s="22" t="n">
-        <v>0.186</v>
+        <v>-423.425</v>
       </c>
       <c r="S171" s="22" t="n">
-        <v>0</v>
+        <v>-833.599</v>
       </c>
       <c r="T171" s="22" t="n">
-        <v>0</v>
+        <v>-390.956</v>
       </c>
       <c r="U171" s="22" t="n">
-        <v>0.9</v>
+        <v>-339.392</v>
       </c>
       <c r="V171" s="22" t="n">
-        <v>0.08</v>
+        <v>-435.475</v>
       </c>
       <c r="W171" s="22" t="n">
-        <v>0</v>
+        <v>-419.969</v>
       </c>
       <c r="X171" s="22" t="n">
-        <v>169.036</v>
+        <v>-536.47</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 이행 지출</t>
-        </is>
-      </c>
-      <c r="G172" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" s="22" t="n">
-        <v>-71.69</v>
-      </c>
-      <c r="M172" s="22" t="n">
-        <v>-71.69</v>
-      </c>
-      <c r="W172" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X172" s="22" t="n">
-        <v>-71.69</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="S172" s="22" t="n">
+        <v>-87.88800000000001</v>
+      </c>
+      <c r="T172" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C173" s="12" t="n">
-        <v>-275.472</v>
-      </c>
-      <c r="E173" s="12" t="n">
-        <v>-571.458</v>
-      </c>
-      <c r="G173" s="12" t="n">
-        <v>-505.343</v>
-      </c>
-      <c r="I173" s="12" t="n">
-        <v>-870.838</v>
-      </c>
-      <c r="K173" s="12" t="n">
-        <v>-451.874</v>
-      </c>
-      <c r="M173" s="12" t="n">
-        <v>-1486.18</v>
-      </c>
-      <c r="R173" s="12" t="n">
-        <v>-684.821</v>
-      </c>
-      <c r="S173" s="12" t="n">
-        <v>-1073.062</v>
-      </c>
-      <c r="T173" s="12" t="n">
-        <v>-477.89</v>
-      </c>
-      <c r="U173" s="12" t="n">
-        <v>-434.418</v>
-      </c>
-      <c r="V173" s="12" t="n">
-        <v>-571.458</v>
-      </c>
-      <c r="W173" s="12" t="n">
-        <v>-870.838</v>
-      </c>
-      <c r="X173" s="12" t="n">
-        <v>-1486.18</v>
+      <c r="A173" s="20" t="inlineStr">
+        <is>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="E173" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" s="22" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="V173" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
+          <t>Collection Of Short Term Loans Receivable Inv CF</t>
         </is>
       </c>
       <c r="C174" s="22" t="n">
-        <v>12.006</v>
+        <v>0</v>
       </c>
       <c r="E174" s="22" t="n">
-        <v>27.318</v>
-      </c>
-      <c r="G174" s="22" t="n">
-        <v>18.444</v>
-      </c>
-      <c r="I174" s="22" t="n">
-        <v>31.494</v>
-      </c>
-      <c r="K174" s="22" t="n">
-        <v>20.184</v>
-      </c>
-      <c r="M174" s="22" t="n">
-        <v>57.68</v>
+        <v>0</v>
+      </c>
+      <c r="R174" s="22" t="n">
+        <v>5.02</v>
       </c>
       <c r="S174" s="22" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="T174" s="22" t="n">
-        <v>504.001</v>
+        <v>5.02</v>
       </c>
       <c r="U174" s="22" t="n">
-        <v>24.534</v>
+        <v>5.02</v>
       </c>
       <c r="V174" s="22" t="n">
-        <v>27.318</v>
-      </c>
-      <c r="W174" s="22" t="n">
-        <v>31.494</v>
-      </c>
-      <c r="X174" s="22" t="n">
-        <v>57.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="C175" s="22" t="n">
-        <v>-0.061</v>
+          <t>유가증권 및 투자유가증권 취득 지출</t>
+        </is>
       </c>
       <c r="E175" s="22" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="G175" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>-311.125</v>
-      </c>
-      <c r="K175" s="22" t="n">
-        <v>-0.08</v>
+        <v>-100</v>
       </c>
       <c r="M175" s="22" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="S175" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T175" s="22" t="n">
-        <v>-0.314</v>
-      </c>
-      <c r="U175" s="22" t="n">
-        <v>-0.478</v>
+        <v>-790.184</v>
       </c>
       <c r="V175" s="22" t="n">
-        <v>-0.061</v>
+        <v>0</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>-311.125</v>
+        <v>-100</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>-0.08</v>
+        <v>-790.184</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
-        </is>
-      </c>
-      <c r="C176" s="22" t="n">
-        <v>-8.975</v>
-      </c>
-      <c r="E176" s="22" t="n">
-        <v>-13.062</v>
-      </c>
-      <c r="G176" s="22" t="n">
-        <v>-4.108</v>
+          <t>투자유가증권 매각·상환 수입</t>
+        </is>
       </c>
       <c r="I176" s="22" t="n">
-        <v>-8.238</v>
-      </c>
-      <c r="K176" s="22" t="n">
-        <v>-65.155</v>
+        <v>0</v>
       </c>
       <c r="M176" s="22" t="n">
-        <v>-65.155</v>
-      </c>
-      <c r="R176" s="22" t="n">
-        <v>-17.518</v>
-      </c>
-      <c r="S176" s="22" t="n">
-        <v>-17.493</v>
-      </c>
-      <c r="T176" s="22" t="n">
-        <v>-17.375</v>
-      </c>
-      <c r="U176" s="22" t="n">
-        <v>-17.73</v>
-      </c>
-      <c r="V176" s="22" t="n">
-        <v>-13.062</v>
+        <v>157.004</v>
       </c>
       <c r="W176" s="22" t="n">
-        <v>-8.238</v>
+        <v>0</v>
       </c>
       <c r="X176" s="22" t="n">
-        <v>-65.155</v>
+        <v>157.004</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>보증금 납입</t>
         </is>
       </c>
       <c r="C177" s="22" t="n">
-        <v>-140.522</v>
+        <v>0</v>
       </c>
       <c r="E177" s="22" t="n">
-        <v>-140.662</v>
+        <v>0</v>
       </c>
       <c r="G177" s="22" t="n">
-        <v>-141.704</v>
+        <v>-110.807</v>
       </c>
       <c r="I177" s="22" t="n">
-        <v>-141.714</v>
+        <v>-111.146</v>
       </c>
       <c r="K177" s="22" t="n">
-        <v>-185.105</v>
+        <v>-0.21</v>
       </c>
       <c r="M177" s="22" t="n">
-        <v>-185.109</v>
+        <v>-0.21</v>
+      </c>
+      <c r="R177" s="22" t="n">
+        <v>-3.483</v>
+      </c>
+      <c r="S177" s="22" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="T177" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="U177" s="22" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="V177" s="22" t="n">
-        <v>-140.662</v>
+        <v>0</v>
       </c>
       <c r="W177" s="22" t="n">
-        <v>-141.714</v>
+        <v>-111.146</v>
       </c>
       <c r="X177" s="22" t="n">
-        <v>-185.109</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C178" s="12" t="n">
-        <v>-137.553</v>
-      </c>
-      <c r="E178" s="12" t="n">
-        <v>-126.468</v>
-      </c>
-      <c r="G178" s="12" t="n">
-        <v>-127.369</v>
-      </c>
-      <c r="I178" s="12" t="n">
-        <v>-429.585</v>
-      </c>
-      <c r="K178" s="12" t="n">
-        <v>-230.158</v>
-      </c>
-      <c r="M178" s="12" t="n">
-        <v>-192.666</v>
-      </c>
-      <c r="R178" s="12" t="n">
-        <v>-17.518</v>
-      </c>
-      <c r="S178" s="12" t="n">
-        <v>-17.493</v>
-      </c>
-      <c r="T178" s="12" t="n">
-        <v>486.31</v>
-      </c>
-      <c r="U178" s="12" t="n">
-        <v>6.325</v>
-      </c>
-      <c r="V178" s="12" t="n">
-        <v>-126.468</v>
-      </c>
-      <c r="W178" s="12" t="n">
-        <v>-429.585</v>
-      </c>
-      <c r="X178" s="12" t="n">
-        <v>-192.666</v>
+      <c r="A178" s="20" t="inlineStr">
+        <is>
+          <t>보증금 회수</t>
+        </is>
+      </c>
+      <c r="C178" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E178" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" s="22" t="n">
+        <v>169.036</v>
+      </c>
+      <c r="M178" s="22" t="n">
+        <v>169.036</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="S178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" s="22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" s="22" t="n">
+        <v>169.036</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
+          <t>자산복구부채 이행 지출</t>
+        </is>
+      </c>
+      <c r="G179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" s="22" t="n">
+        <v>-71.69</v>
+      </c>
+      <c r="M179" s="22" t="n">
+        <v>-71.69</v>
+      </c>
+      <c r="W179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X179" s="22" t="n">
+        <v>-71.69</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="n">
+        <v>-275.472</v>
+      </c>
+      <c r="E180" s="12" t="n">
+        <v>-571.458</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>-505.343</v>
+      </c>
+      <c r="I180" s="12" t="n">
+        <v>-870.838</v>
+      </c>
+      <c r="K180" s="12" t="n">
+        <v>-451.874</v>
+      </c>
+      <c r="M180" s="12" t="n">
+        <v>-1486.18</v>
+      </c>
+      <c r="R180" s="12" t="n">
+        <v>-684.821</v>
+      </c>
+      <c r="S180" s="12" t="n">
+        <v>-1073.062</v>
+      </c>
+      <c r="T180" s="12" t="n">
+        <v>-477.89</v>
+      </c>
+      <c r="U180" s="12" t="n">
+        <v>-434.418</v>
+      </c>
+      <c r="V180" s="12" t="n">
+        <v>-571.458</v>
+      </c>
+      <c r="W180" s="12" t="n">
+        <v>-870.838</v>
+      </c>
+      <c r="X180" s="12" t="n">
+        <v>-1486.18</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="20" t="inlineStr">
+        <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="n">
+        <v>12.006</v>
+      </c>
+      <c r="E181" s="22" t="n">
+        <v>27.318</v>
+      </c>
+      <c r="G181" s="22" t="n">
+        <v>18.444</v>
+      </c>
+      <c r="I181" s="22" t="n">
+        <v>31.494</v>
+      </c>
+      <c r="K181" s="22" t="n">
+        <v>20.184</v>
+      </c>
+      <c r="M181" s="22" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="S181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" s="22" t="n">
+        <v>504.001</v>
+      </c>
+      <c r="U181" s="22" t="n">
+        <v>24.534</v>
+      </c>
+      <c r="V181" s="22" t="n">
+        <v>27.318</v>
+      </c>
+      <c r="W181" s="22" t="n">
+        <v>31.494</v>
+      </c>
+      <c r="X181" s="22" t="n">
+        <v>57.68</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C182" s="22" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="E182" s="22" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="22" t="n">
+        <v>-311.125</v>
+      </c>
+      <c r="K182" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M182" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="S182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" s="22" t="n">
+        <v>-0.314</v>
+      </c>
+      <c r="U182" s="22" t="n">
+        <v>-0.478</v>
+      </c>
+      <c r="V182" s="22" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="W182" s="22" t="n">
+        <v>-311.125</v>
+      </c>
+      <c r="X182" s="22" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="C183" s="22" t="n">
+        <v>-8.975</v>
+      </c>
+      <c r="E183" s="22" t="n">
+        <v>-13.062</v>
+      </c>
+      <c r="G183" s="22" t="n">
+        <v>-4.108</v>
+      </c>
+      <c r="I183" s="22" t="n">
+        <v>-8.238</v>
+      </c>
+      <c r="K183" s="22" t="n">
+        <v>-65.155</v>
+      </c>
+      <c r="M183" s="22" t="n">
+        <v>-65.155</v>
+      </c>
+      <c r="R183" s="22" t="n">
+        <v>-17.518</v>
+      </c>
+      <c r="S183" s="22" t="n">
+        <v>-17.493</v>
+      </c>
+      <c r="T183" s="22" t="n">
+        <v>-17.375</v>
+      </c>
+      <c r="U183" s="22" t="n">
+        <v>-17.73</v>
+      </c>
+      <c r="V183" s="22" t="n">
+        <v>-13.062</v>
+      </c>
+      <c r="W183" s="22" t="n">
+        <v>-8.238</v>
+      </c>
+      <c r="X183" s="22" t="n">
+        <v>-65.155</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C184" s="22" t="n">
+        <v>-140.522</v>
+      </c>
+      <c r="E184" s="22" t="n">
+        <v>-140.662</v>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>-141.704</v>
+      </c>
+      <c r="I184" s="22" t="n">
+        <v>-141.714</v>
+      </c>
+      <c r="K184" s="22" t="n">
+        <v>-185.105</v>
+      </c>
+      <c r="M184" s="22" t="n">
+        <v>-185.109</v>
+      </c>
+      <c r="U184" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" s="22" t="n">
+        <v>-140.662</v>
+      </c>
+      <c r="W184" s="22" t="n">
+        <v>-141.714</v>
+      </c>
+      <c r="X184" s="22" t="n">
+        <v>-185.109</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="n">
+        <v>-137.553</v>
+      </c>
+      <c r="E185" s="12" t="n">
+        <v>-126.468</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>-127.369</v>
+      </c>
+      <c r="I185" s="12" t="n">
+        <v>-429.585</v>
+      </c>
+      <c r="K185" s="12" t="n">
+        <v>-230.158</v>
+      </c>
+      <c r="M185" s="12" t="n">
+        <v>-192.666</v>
+      </c>
+      <c r="R185" s="12" t="n">
+        <v>-17.518</v>
+      </c>
+      <c r="S185" s="12" t="n">
+        <v>-17.493</v>
+      </c>
+      <c r="T185" s="12" t="n">
+        <v>486.31</v>
+      </c>
+      <c r="U185" s="12" t="n">
+        <v>6.325</v>
+      </c>
+      <c r="V185" s="12" t="n">
+        <v>-126.468</v>
+      </c>
+      <c r="W185" s="12" t="n">
+        <v>-429.585</v>
+      </c>
+      <c r="X185" s="12" t="n">
+        <v>-192.666</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 환산차이</t>
         </is>
       </c>
-      <c r="C179" s="22" t="n">
+      <c r="C186" s="22" t="n">
         <v>1.499</v>
       </c>
-      <c r="E179" s="22" t="n">
+      <c r="E186" s="22" t="n">
         <v>1.49</v>
       </c>
-      <c r="G179" s="22" t="n">
+      <c r="G186" s="22" t="n">
         <v>0.365</v>
       </c>
-      <c r="I179" s="22" t="n">
+      <c r="I186" s="22" t="n">
         <v>-2.673</v>
       </c>
-      <c r="K179" s="22" t="n">
+      <c r="K186" s="22" t="n">
         <v>-0.954</v>
       </c>
-      <c r="M179" s="22" t="n">
+      <c r="M186" s="22" t="n">
         <v>-0.291</v>
       </c>
-      <c r="R179" s="22" t="n">
+      <c r="R186" s="22" t="n">
         <v>-0.027</v>
       </c>
-      <c r="S179" s="22" t="n">
+      <c r="S186" s="22" t="n">
         <v>0.149</v>
       </c>
-      <c r="T179" s="22" t="n">
+      <c r="T186" s="22" t="n">
         <v>2.103</v>
       </c>
-      <c r="U179" s="22" t="n">
+      <c r="U186" s="22" t="n">
         <v>2.643</v>
       </c>
-      <c r="V179" s="22" t="n">
+      <c r="V186" s="22" t="n">
         <v>1.49</v>
       </c>
-      <c r="W179" s="22" t="n">
+      <c r="W186" s="22" t="n">
         <v>-2.673</v>
       </c>
-      <c r="X179" s="22" t="n">
+      <c r="X186" s="22" t="n">
         <v>-0.291</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="20" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="20" t="inlineStr">
         <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C180" s="22" t="n">
+      <c r="C187" s="22" t="n">
         <v>282.183</v>
       </c>
-      <c r="E180" s="22" t="n">
+      <c r="E187" s="22" t="n">
         <v>525.409</v>
       </c>
-      <c r="G180" s="22" t="n">
+      <c r="G187" s="22" t="n">
         <v>866.665</v>
       </c>
-      <c r="I180" s="22" t="n">
+      <c r="I187" s="22" t="n">
         <v>690.228</v>
       </c>
-      <c r="K180" s="22" t="n">
+      <c r="K187" s="22" t="n">
         <v>274.913</v>
       </c>
-      <c r="M180" s="22" t="n">
+      <c r="M187" s="22" t="n">
         <v>-125.859</v>
       </c>
-      <c r="R180" s="22" t="n">
+      <c r="R187" s="22" t="n">
         <v>109.535</v>
       </c>
-      <c r="S180" s="22" t="n">
+      <c r="S187" s="22" t="n">
         <v>28.861</v>
       </c>
-      <c r="T180" s="22" t="n">
+      <c r="T187" s="22" t="n">
         <v>1614.973</v>
       </c>
-      <c r="U180" s="22" t="n">
+      <c r="U187" s="22" t="n">
         <v>788.4160000000001</v>
       </c>
-      <c r="V180" s="22" t="n">
+      <c r="V187" s="22" t="n">
         <v>525.409</v>
       </c>
-      <c r="W180" s="22" t="n">
+      <c r="W187" s="22" t="n">
         <v>690.228</v>
       </c>
-      <c r="X180" s="22" t="n">
+      <c r="X187" s="22" t="n">
         <v>-125.859</v>
       </c>
     </row>
@@ -9947,7 +10418,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11341,7 +11812,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11393,7 +11864,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11445,7 +11916,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11497,7 +11968,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11549,7 +12020,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11601,7 +12072,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11653,7 +12124,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11663,43 +12134,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11723,7 +12194,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11775,7 +12246,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11827,7 +12298,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11879,7 +12350,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11931,7 +12402,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11983,7 +12454,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12053,7 +12524,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12105,7 +12576,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12115,49 +12586,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12167,49 +12638,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12219,49 +12690,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12271,43 +12742,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12331,7 +12802,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12383,7 +12854,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12435,7 +12906,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12487,7 +12958,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15191,24 +15662,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
